--- a/stories/arbres/TREE-COL-028.xlsx
+++ b/stories/arbres/TREE-COL-028.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Zoé est avec papa, sur le chemin de l'école. Zoé a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé écoute papa. Zoé entend les mots : bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Zoé va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-028.xlsx
+++ b/stories/arbres/TREE-COL-028.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Zoé est avec papa, sur le chemin de l'école. Zoé a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé écoute papa. Zoé entend les mots : bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Zoé a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Zoé rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Zoé rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Zoé a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Zoé a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Zoé rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Zoé a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Zoé a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Zoé rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Zoé a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Zoé a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Zoé rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Zoé a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Zoé a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Zoé rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Zoé rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Zoé rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-028.xlsx
+++ b/stories/arbres/TREE-COL-028.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bonjour, s'il te plaît, merci — sur le chemin de l'école</t>
+          <t>Le cartable jaune près de la vitre</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le cartable jaune attend près de la vitre embuée. Nina dit bonjour, s'il te plaît, merci, dans la maison au bord du chemin de l'école, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Zoé est avec papa, sur le chemin de l'école. Zoé a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé écoute papa. Zoé entend les mots : bonjour, s'il te plaît, merci.</t>
+          <t>La vitre de la cuisine est toute embuée. Un petit escargot dessine un fil d'argent. Le cartable jaune pend près du radiateur. Dehors, le chemin de l'école brille encore. Une gouttière fait plic, tout lent. Ça sent le pain grillé. Les clés de papa sont sur la table. Elles sont froides, un peu. Maman essuie la vitre d'un coin de torchon. Un rond de jardin apparaît, tout vert. Nina, tu as vu l'escargot ? Il va tout doux. Oui. Il laisse un fil brillant. En ce moment, Nina pose un doigt sur la vitre. Le verre est froid, tout lisse. On dit bonjour, d'accord ? Bonjour. Si tu veux le cartable ? S'il te plaît. Et après ? Merci. Bravo, Nina. Tu as les trois mots. Bonjour. S'il te plaît. Merci. Le chemin de l'école attend, dehors. Ici, on est encore à la maison. Oui, papa. L'escargot avance. Le fil d'argent reste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,44 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Zoé est avec papa, sur le chemin de l'école. Zoé a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé écoute papa. Zoé entend les mots : bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|Un petit escargot dessine un fil d'argent.
+narrateur|Le cartable jaune pend près du radiateur.
+narrateur|Dehors, le chemin de l'école brille encore.
+narrateur|Une gouttière fait plic, tout lent.
+narrateur|Ça sent le pain grillé.
+narrateur|Les clés de papa sont sur la table.
+narrateur|Elles sont froides, un peu.
+narrateur|Maman essuie la vitre d'un coin de torchon.
+narrateur|Un rond de jardin apparaît, tout vert.
+papa|Nina, tu as vu l'escargot ?
+enfant-f|Il va tout doux.
+maman|Oui.
+maman|Il laisse un fil brillant.
+narrateur|En ce moment, Nina pose un doigt sur la vitre.
+narrateur|Le verre est froid, tout lisse.
+maman|On dit bonjour, d'accord ?
+enfant-f|Bonjour.
+papa|Si tu veux le cartable ?
+enfant-f|S'il te plaît.
+maman|Et après ?
+enfant-f|Merci.
+papa|Bravo, Nina.
+papa|Tu as les trois mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Le chemin de l'école attend, dehors.
+papa|Ici, on est encore à la maison.
+enfant-f|Oui, papa.
+narrateur|L'escargot avance. Le fil d'argent reste.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>gouttiere,fenetre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>La maison a trois endroits tout proches. La cuisine, le jardin, ou la chambre ? On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1563,11 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|La maison a trois endroits tout proches.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On dit bonjour.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers la cuisine. Le carrelage est froid sous les chaussettes. Des miettes dorées attendent près du bol. La bouilloire fait un petit chuintement. La vitre est encore un peu embuée. Nina, on dit bonjour. Bonjour. Bonjour. Tu veux une miette ? S'il te plaît. Papa tend un bout de croûte. La croûte est tiède, un peu rêche. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le cartable jaune se voit depuis la table. On reste un moment, ici. Ça sent le pain. Oui. Ça sent le grillé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1735,36 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers la cuisine. Le vent est doux. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On se tient la main.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina va vers la cuisine.
+narrateur|Le carrelage est froid sous les chaussettes.
+narrateur|Des miettes dorées attendent près du bol.
+narrateur|La bouilloire fait un petit chuintement.
+narrateur|La vitre est encore un peu embuée.
+papa|Nina, on dit bonjour.
+enfant-f|Bonjour.
+maman|Bonjour.
+papa|Tu veux une miette ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend un bout de croûte.
+narrateur|La croûte est tiède, un peu rêche.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le cartable jaune se voit depuis la table.
+maman|On reste un moment, ici.
+enfant-f|Ça sent le pain.
+papa|Oui.
+papa|Ça sent le grillé.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>bouilloire,miettes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Nina demande, dans la cuisine. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1949,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Nina demande, dans la cuisine.
+maman|Que dit-elle ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1978,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. Bonjour. S'il te plaît. Merci. Nina souffle un peu. Une miette reste sur le bol. J'ai dit les mots. Bravo, Nina. Tu as fait du bon travail. La bouilloire se tait, tout doux. On continue, avec papa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2122,17 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>maman|Oui.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Nina souffle un peu.
+narrateur|Une miette reste sur le bol.
+enfant-f|J'ai dit les mots.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+narrateur|La bouilloire se tait, tout doux.
+maman|On continue, avec papa.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2160,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jouets attendent, tout calmes. Les cubes, le livre, ou la dînette ? On demande, avec les mots.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2324,9 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jouets attendent, tout calmes.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande, avec les mots.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2354,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+          <t>Nina a choisi les cubes. Le bois est lisse, un peu tiède. Deux cubes font clic, tout doux. Tu veux le cube rouge ? S'il te plaît. Papa pose le cube rouge. Merci. Bonjour, cube. Bravo, Nina. Tu as dit les trois mots. On souffle un peu. Un cube bleu attend, tout calme. Un cube a une miette collée, tout dorée. On est encore dans la cuisine. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2494,32 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nina a choisi les cubes.
+narrateur|Le bois est lisse, un peu tiède.
+narrateur|Deux cubes font clic, tout doux.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa pose le cube rouge.
+enfant-f|Merci.
+enfant-f|Bonjour, cube.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On souffle un peu.
+narrateur|Un cube bleu attend, tout calme.
+narrateur|Un cube a une miette collée, tout dorée.
+narrateur|On est encore dans la cuisine.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2544,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2708,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2738,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a les cubes, dans la cuisine. Un cube rouge attrape le soleil, sur la table. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,10 +2878,31 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. La lumière est claire. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a les cubes, dans la cuisine.
+narrateur|Un cube rouge attrape le soleil, sur la table.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2794,7 +2927,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la cuisine. Elle a joué avec les cubes. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3067,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3104,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a les cubes, dans la cuisine. Un cube bleu dort près des miettes. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3244,24 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a les cubes, dans la cuisine.
+narrateur|Un cube bleu dort près des miettes.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3289,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la cuisine. Elle a joué avec les cubes. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3429,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3466,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a les cubes, dans la cuisine. La lampe pose un rond sur le cube rouge. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,10 +3606,31 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a les cubes, dans la cuisine.
+narrateur|La lampe pose un rond sur le cube rouge.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3466,7 +3655,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la cuisine. Elle a joué avec les cubes. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3795,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3832,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Nina a choisi le livre. Les pages sont épaisses, un peu rudes. Un oiseau est dessiné, tout jaune. Tu veux ouvrir le livre ? S'il te plaît. Maman tourne une page, tout lent. Merci. Bonjour, oiseau. Bravo, Nina. Tu as dit les trois mots. On écoute jusqu'au bout. Le papier sent un peu le bois. Le livre est près du bol. Ça sent le pain. On est encore dans la cuisine. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3972,33 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le livre.
+narrateur|Les pages sont épaisses, un peu rudes.
+narrateur|Un oiseau est dessiné, tout jaune.
+maman|Tu veux ouvrir le livre ?
+enfant-f|S'il te plaît.
+narrateur|Maman tourne une page, tout lent.
+enfant-f|Merci.
+enfant-f|Bonjour, oiseau.
+papa|Bravo, Nina.
+papa|Tu as dit les trois mots.
+maman|On écoute jusqu'au bout.
+narrateur|Le papier sent un peu le bois.
+narrateur|Le livre est près du bol.
+narrateur|Ça sent le pain.
+narrateur|On est encore dans la cuisine.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +4023,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3966,7 +4187,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3994,7 +4217,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a le livre, dans la cuisine. L'oiseau du livre est jaune, comme le cartable. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,10 +4357,31 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la cuisine, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a le livre, dans la cuisine.
+narrateur|L'oiseau du livre est jaune, comme le cartable.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4162,7 +4406,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la cuisine. Elle a joué avec le livre. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,7 +4546,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4330,7 +4583,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a le livre, dans la cuisine. Une page du livre sent encore le pain. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,7 +4723,24 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a le livre, dans la cuisine.
+narrateur|Une page du livre sent encore le pain.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4498,7 +4768,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la cuisine. Elle a joué avec le livre. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,7 +4908,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4666,7 +4945,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a le livre, dans la cuisine. La lampe éclaire l'oiseau, tout doux. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,10 +5085,31 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a le livre, dans la cuisine.
+narrateur|La lampe éclaire l'oiseau, tout doux.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4834,7 +5134,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la cuisine. Elle a joué avec le livre. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,7 +5274,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5002,7 +5311,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Nina a choisi la dînette. Une petite tasse est bleue, toute ronde. Une soucoupe fait un bruit léger. Tu veux la tasse ? S'il te plaît. Papa tend la tasse, tout doux. Merci. Bonjour. Bravo, Nina. Tu as dit les trois mots. On attend son tour, même pour le thé. La tasse est lisse, un peu froide. La petite tasse est près de la vraie bouilloire. On est encore dans la cuisine. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,10 +5451,32 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Nina a choisi la dînette.
+narrateur|Une petite tasse est bleue, toute ronde.
+narrateur|Une soucoupe fait un bruit léger.
+papa|Tu veux la tasse ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend la tasse, tout doux.
+enfant-f|Merci.
+enfant-f|Bonjour.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On attend son tour, même pour le thé.
+narrateur|La tasse est lisse, un peu froide.
+narrateur|La petite tasse est près de la vraie bouilloire.
+narrateur|On est encore dans la cuisine.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5170,7 +5501,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5334,7 +5665,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5362,7 +5695,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a la dînette, dans la cuisine. La tasse bleue est près du bol, au matin. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,10 +5835,31 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a la dînette, dans la cuisine.
+narrateur|La tasse bleue est près du bol, au matin.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5530,7 +5884,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la cuisine. Elle a joué avec la dînette. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,7 +6024,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5698,7 +6061,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a la dînette, dans la cuisine. Une miette est dans la petite tasse. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,7 +6201,24 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a la dînette, dans la cuisine.
+narrateur|Une miette est dans la petite tasse.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5866,7 +6246,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la cuisine. Elle a joué avec la dînette. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,7 +6386,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6034,7 +6423,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a la dînette, dans la cuisine. La tasse brille sous la lampe, tout calme. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,10 +6563,31 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a la dînette, dans la cuisine.
+narrateur|La tasse brille sous la lampe, tout calme.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6202,7 +6612,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la cuisine. Elle a joué avec la dînette. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,7 +6752,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6370,7 +6789,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers le jardin. L'herbe est froide, encore mouillée. L'arrosoir penche près de la haie. Le chemin de l'école brille, derrière le portail. Une gouttière fait plic, tout lent. On dit bonjour, au jardin. Bonjour. Bonjour. Tu veux l'arrosoir ? S'il te plaît. Papa pose l'arrosoir près des bottes. Le métal est froid, un peu vert. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Un oiseau picore près d'une flaque. On reste près de la haie. L'herbe chatouille. Oui. Elle est toute mouillée.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,11 +6929,36 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers le jardin. Le sol est un peu froid. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Nina va vers le jardin.
+narrateur|L'herbe est froide, encore mouillée.
+narrateur|L'arrosoir penche près de la haie.
+narrateur|Le chemin de l'école brille, derrière le portail.
+narrateur|Une gouttière fait plic, tout lent.
+maman|On dit bonjour, au jardin.
+enfant-f|Bonjour.
+papa|Bonjour.
+maman|Tu veux l'arrosoir ?
+enfant-f|S'il te plaît.
+narrateur|Papa pose l'arrosoir près des bottes.
+narrateur|Le métal est froid, un peu vert.
+enfant-f|Merci.
+papa|Bravo, Nina.
+papa|Tu as dit les trois mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Un oiseau picore près d'une flaque.
+papa|On reste près de la haie.
+enfant-f|L'herbe chatouille.
+maman|Oui.
+maman|Elle est toute mouillée.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>gouttiere,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6539,7 +6983,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Au jardin, Nina parle. Quels mots ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,7 +7143,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Au jardin, Nina parle.
+papa|Quels mots ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6727,7 +7172,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. Bonjour. S'il te plaît. Merci. Nina pose un doigt sur l'herbe. L'herbe est froide, toute verte. Les trois mots. Bravo. C'est du bon travail. La gouttière fait encore plic. On continue ensemble.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,7 +7316,17 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Nina pose un doigt sur l'herbe.
+narrateur|L'herbe est froide, toute verte.
+enfant-f|Les trois mots.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|La gouttière fait encore plic.
+papa|On continue ensemble.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6899,7 +7354,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jouets attendent, tout calmes. Les cubes, le livre, ou la dînette ? On demande, avec les mots.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7063,7 +7518,9 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jouets attendent, tout calmes.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande, avec les mots.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7091,7 +7548,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+          <t>Nina a choisi les cubes. Le bois est lisse, un peu tiède. Deux cubes font clic, tout doux. Tu veux le cube rouge ? S'il te plaît. Papa pose le cube rouge. Merci. Bonjour, cube. Bravo, Nina. Tu as dit les trois mots. On souffle un peu. Un cube bleu attend, tout calme. Un cube a une goutte d'herbe, toute verte. On est encore dans le jardin. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,10 +7688,32 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi les cubes. La lumière est claire. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nina a choisi les cubes.
+narrateur|Le bois est lisse, un peu tiède.
+narrateur|Deux cubes font clic, tout doux.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa pose le cube rouge.
+enfant-f|Merci.
+enfant-f|Bonjour, cube.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On souffle un peu.
+narrateur|Un cube bleu attend, tout calme.
+narrateur|Un cube a une goutte d'herbe, toute verte.
+narrateur|On est encore dans le jardin.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7259,7 +7738,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7423,7 +7902,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7451,7 +7932,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a les cubes, dans le jardin. Un cube a de la rosée, toute froide. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,10 +8072,31 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le jardin, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a les cubes, dans le jardin.
+narrateur|Un cube a de la rosée, toute froide.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7619,7 +8121,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans le jardin. Elle a joué avec les cubes. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,7 +8261,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7787,7 +8298,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a les cubes, dans le jardin. Un cube sèche au soleil, après la sieste. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,7 +8438,24 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a les cubes, dans le jardin.
+narrateur|Un cube sèche au soleil, après la sieste.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7955,7 +8483,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans le jardin. Elle a joué avec les cubes. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,7 +8623,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8123,7 +8660,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a les cubes, dans le jardin. Un cube bleu est dans l'ombre, près de la haie. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,10 +8800,31 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a les cubes, dans le jardin.
+narrateur|Un cube bleu est dans l'ombre, près de la haie.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8291,7 +8849,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans le jardin. Elle a joué avec les cubes. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,7 +8989,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8459,7 +9026,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Nina a choisi le livre. Les pages sont épaisses, un peu rudes. Un oiseau est dessiné, tout jaune. Tu veux ouvrir le livre ? S'il te plaît. Maman tourne une page, tout lent. Merci. Bonjour, oiseau. Bravo, Nina. Tu as dit les trois mots. On écoute jusqu'au bout. Le papier sent un peu le bois. Le livre repose sur une pierre, un peu froide. On est encore dans le jardin. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,10 +9166,32 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le livre. Il y a des miettes sur la table. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le livre.
+narrateur|Les pages sont épaisses, un peu rudes.
+narrateur|Un oiseau est dessiné, tout jaune.
+maman|Tu veux ouvrir le livre ?
+enfant-f|S'il te plaît.
+narrateur|Maman tourne une page, tout lent.
+enfant-f|Merci.
+enfant-f|Bonjour, oiseau.
+papa|Bravo, Nina.
+papa|Tu as dit les trois mots.
+maman|On écoute jusqu'au bout.
+narrateur|Le papier sent un peu le bois.
+narrateur|Le livre repose sur une pierre, un peu froide.
+narrateur|On est encore dans le jardin.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8627,7 +9216,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8791,7 +9380,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8819,7 +9410,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a le livre, dans le jardin. Le livre a une goutte, sur la pierre. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,10 +9550,31 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le jardin, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a le livre, dans le jardin.
+narrateur|Le livre a une goutte, sur la pierre.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8987,7 +9599,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans le jardin. Elle a joué avec le livre. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,7 +9739,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9155,7 +9776,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a le livre, dans le jardin. Un oiseau vrai picore, près du livre. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,7 +9916,24 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a le livre, dans le jardin.
+narrateur|Un oiseau vrai picore, près du livre.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9323,7 +9961,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans le jardin. Elle a joué avec le livre. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,7 +10101,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9491,7 +10138,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a le livre, dans le jardin. Le livre se ferme. La gouttière fait plic. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,10 +10278,32 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a le livre, dans le jardin.
+narrateur|Le livre se ferme.
+narrateur|La gouttière fait plic.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9659,7 +10328,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans le jardin. Elle a joué avec le livre. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,7 +10468,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9827,7 +10505,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Nina a choisi la dînette. Une petite tasse est bleue, toute ronde. Une soucoupe fait un bruit léger. Tu veux la tasse ? S'il te plaît. Papa tend la tasse, tout doux. Merci. Bonjour. Bravo, Nina. Tu as dit les trois mots. On attend son tour, même pour le thé. La tasse est lisse, un peu froide. La tasse a une feuille collée, tout léger. On est encore dans le jardin. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,10 +10645,32 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi la dînette. Un chat miaule une fois. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Nina a choisi la dînette.
+narrateur|Une petite tasse est bleue, toute ronde.
+narrateur|Une soucoupe fait un bruit léger.
+papa|Tu veux la tasse ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend la tasse, tout doux.
+enfant-f|Merci.
+enfant-f|Bonjour.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On attend son tour, même pour le thé.
+narrateur|La tasse est lisse, un peu froide.
+narrateur|La tasse a une feuille collée, tout léger.
+narrateur|On est encore dans le jardin.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9995,7 +10695,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10159,7 +10859,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10187,7 +10889,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a la dînette, dans le jardin. La tasse a une feuille de rosée, tout petit. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,10 +11029,31 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le jardin, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a la dînette, dans le jardin.
+narrateur|La tasse a une feuille de rosée, tout petit.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10355,7 +11078,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans le jardin. Elle a joué avec la dînette. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,7 +11218,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10523,7 +11255,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a la dînette, dans le jardin. La tasse est tiède, après la sieste au jardin. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,7 +11395,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a la dînette, dans le jardin.
+narrateur|La tasse est tiède, après la sieste au jardin.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10691,7 +11440,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans le jardin. Elle a joué avec la dînette. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,7 +11580,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10859,7 +11617,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a la dînette, dans le jardin. La tasse est froide. Un oiseau se tait. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,10 +11757,32 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a la dînette, dans le jardin.
+narrateur|La tasse est froide.
+narrateur|Un oiseau se tait.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11027,7 +11807,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans le jardin. Elle a joué avec la dînette. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,7 +11947,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11195,7 +11984,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Zoé va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Nina va vers la chambre. La couverture est douce, un peu froissée. Un rideau jaune bouge, tout léger. Le cartable attend au pied du lit. Un doudou est sur l'oreiller, tout calme. On dit bonjour, Nina. Bonjour. Bonjour. Tu veux le doudou ? S'il te plaît. Maman tend le doudou, tout doux. Une oreille est encore chaude. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le bois du lit est lisse sous la main. On reste un moment, ici. Le doudou est chaud. Oui. Il t'attendait.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,8 +12124,29 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Zoé va vers la chambre. Une feuille tombe. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Zoé se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Nina va vers la chambre.
+narrateur|La couverture est douce, un peu froissée.
+narrateur|Un rideau jaune bouge, tout léger.
+narrateur|Le cartable attend au pied du lit.
+narrateur|Un doudou est sur l'oreiller, tout calme.
+papa|On dit bonjour, Nina.
+enfant-f|Bonjour.
+maman|Bonjour.
+papa|Tu veux le doudou ?
+enfant-f|S'il te plaît.
+narrateur|Maman tend le doudou, tout doux.
+narrateur|Une oreille est encore chaude.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le bois du lit est lisse sous la main.
+maman|On reste un moment, ici.
+enfant-f|Le doudou est chaud.
+papa|Oui.
+papa|Il t'attendait.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11364,7 +12174,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Dans la chambre, Nina a parlé. On dit merci, après ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11524,7 +12334,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Dans la chambre, Nina a parlé.
+maman|On dit merci, après ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11552,7 +12363,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. Bonjour. S'il te plaît. Merci. Nina serre le doudou, tout calme. Le rideau jaune bouge encore. Merci, maman. Bravo, Nina. Tu as dit les mots. Le cartable reste au pied du lit.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11696,7 +12507,16 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Zoé respire. Zoé retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>maman|Oui.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Nina serre le doudou, tout calme.
+narrateur|Le rideau jaune bouge encore.
+enfant-f|Merci, maman.
+papa|Bravo, Nina.
+papa|Tu as dit les mots.
+narrateur|Le cartable reste au pied du lit.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11724,7 +12544,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jouets attendent, tout calmes. Les cubes, le livre, ou la dînette ? On demande, avec les mots.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11888,7 +12708,9 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jouets attendent, tout calmes.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande, avec les mots.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11916,7 +12738,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
+          <t>Nina a choisi les cubes. Le bois est lisse, un peu tiède. Deux cubes font clic, tout doux. Tu veux le cube rouge ? S'il te plaît. Papa pose le cube rouge. Merci. Bonjour, cube. Bravo, Nina. Tu as dit les trois mots. On souffle un peu. Un cube bleu attend, tout calme. Un cube rouge est sur le tapis, près du doudou. On est encore dans la chambre. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,10 +12878,32 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Nina a choisi les cubes.
+narrateur|Le bois est lisse, un peu tiède.
+narrateur|Deux cubes font clic, tout doux.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa pose le cube rouge.
+enfant-f|Merci.
+enfant-f|Bonjour, cube.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On souffle un peu.
+narrateur|Un cube bleu attend, tout calme.
+narrateur|Un cube rouge est sur le tapis, près du doudou.
+narrateur|On est encore dans la chambre.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12084,7 +12928,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12248,7 +13092,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12276,7 +13122,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a les cubes, dans la chambre. Un cube rouge touche le cartable jaune. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,10 +13262,31 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la chambre, les cubes et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a les cubes, dans la chambre.
+narrateur|Un cube rouge touche le cartable jaune.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12444,7 +13311,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la chambre. Elle a joué avec les cubes. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,7 +13451,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12612,7 +13488,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a les cubes, dans la chambre. Un cube est contre l'oreiller, tout calme. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,7 +13628,24 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a les cubes, dans la chambre.
+narrateur|Un cube est contre l'oreiller, tout calme.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12780,7 +13673,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la chambre. Elle a joué avec les cubes. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,7 +13813,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12948,7 +13850,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a les cubes, dans la chambre. Un cube brille sous la lampe, près du doudou. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,10 +13990,31 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a les cubes, dans la chambre.
+narrateur|Un cube brille sous la lampe, près du doudou.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13116,7 +14039,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la chambre. Elle a joué avec les cubes. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,7 +14179,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13284,7 +14216,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Nina a choisi le livre. Les pages sont épaisses, un peu rudes. Un oiseau est dessiné, tout jaune. Tu veux ouvrir le livre ? S'il te plaît. Maman tourne une page, tout lent. Merci. Bonjour, oiseau. Bravo, Nina. Tu as dit les trois mots. On écoute jusqu'au bout. Le papier sent un peu le bois. Le livre est sur l'oreiller, tout calme. On est encore dans la chambre. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,10 +14356,32 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nina a choisi le livre.
+narrateur|Les pages sont épaisses, un peu rudes.
+narrateur|Un oiseau est dessiné, tout jaune.
+maman|Tu veux ouvrir le livre ?
+enfant-f|S'il te plaît.
+narrateur|Maman tourne une page, tout lent.
+enfant-f|Merci.
+enfant-f|Bonjour, oiseau.
+papa|Bravo, Nina.
+papa|Tu as dit les trois mots.
+maman|On écoute jusqu'au bout.
+narrateur|Le papier sent un peu le bois.
+narrateur|Le livre est sur l'oreiller, tout calme.
+narrateur|On est encore dans la chambre.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13452,7 +14406,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13616,7 +14570,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13644,7 +14600,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a le livre, dans la chambre. Le livre est près du cartable, tout prêt. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,10 +14740,31 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la chambre, le livre et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a le livre, dans la chambre.
+narrateur|Le livre est près du cartable, tout prêt.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13812,7 +14789,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la chambre. Elle a joué avec le livre. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,7 +14929,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13980,7 +14966,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a le livre, dans la chambre. Le livre reste ouvert sur l'oreiller chaud. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,7 +15106,24 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a le livre, dans la chambre.
+narrateur|Le livre reste ouvert sur l'oreiller chaud.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14148,7 +15151,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la chambre. Elle a joué avec le livre. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,7 +15291,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14316,7 +15328,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a le livre, dans la chambre. Le livre se ferme. Le rideau jaune s'arrête. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,10 +15468,32 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a le livre, dans la chambre.
+narrateur|Le livre se ferme.
+narrateur|Le rideau jaune s'arrête.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14484,7 +15518,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la chambre. Elle a joué avec le livre. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,7 +15658,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14652,7 +15695,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Zoé a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Nina a choisi la dînette. Une petite tasse est bleue, toute ronde. Une soucoupe fait un bruit léger. Tu veux la tasse ? S'il te plaît. Papa tend la tasse, tout doux. Merci. Bonjour. Bravo, Nina. Tu as dit les trois mots. On attend son tour, même pour le thé. La tasse est lisse, un peu froide. La tasse est près de la couverture douce. On est encore dans la chambre. On dit les trois mots. Bonjour. S'il te plaît. Merci. C'est du bon travail, Nina.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,10 +15835,32 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Zoé répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Nina a choisi la dînette.
+narrateur|Une petite tasse est bleue, toute ronde.
+narrateur|Une soucoupe fait un bruit léger.
+papa|Tu veux la tasse ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend la tasse, tout doux.
+enfant-f|Merci.
+enfant-f|Bonjour.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|On attend son tour, même pour le thé.
+narrateur|La tasse est lisse, un peu froide.
+narrateur|La tasse est près de la couverture douce.
+narrateur|On est encore dans la chambre.
+maman|On dit les trois mots.
+enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|C'est du bon travail, Nina.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>tasse</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14820,7 +15885,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Le jour a trois moments. Le matin, après la sieste, ou le soir ? Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,7 +16049,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Le jour a trois moments.
+papa|Le matin, après la sieste, ou le soir ?
+maman|Les mots restent les mêmes.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15012,7 +16079,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est claire, un peu pâle. Le cartable jaune attend déjà. Nina a la dînette, dans la chambre. La tasse est près du cartable, au matin. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,10 +16219,31 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de la chambre, la dînette et le matin. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est claire, un peu pâle.
+narrateur|Le cartable jaune attend déjà.
+narrateur|Nina a la dînette, dans la chambre.
+narrateur|La tasse est près du cartable, au matin.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15180,7 +16268,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le matin, dans la chambre. Elle a joué avec la dînette. Le cartable jaune attend encore, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +16408,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|Le cartable jaune attend encore, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +16445,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Une joue de Nina est encore chaude. Les cheveux sont un peu en désordre. Nina a la dînette, dans la chambre. La tasse est sur la couverture, tout douce. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +16585,24 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et après la sieste. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>narrateur|C'est après la sieste.
+narrateur|Une joue de Nina est encore chaude.
+narrateur|Les cheveux sont un peu en désordre.
+narrateur|Nina a la dînette, dans la chambre.
+narrateur|La tasse est sur la couverture, tout douce.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16630,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu après la sieste, dans la chambre. Elle a joué avec la dînette. La joue de Nina n'est plus si chaude. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16770,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|La joue de Nina n'est plus si chaude.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16807,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Zoé rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. Une petite lampe fait un rond jaune. Les chaussons sont près de la porte. Nina a la dînette, dans la chambre. La tasse est près des chaussons, sous la lampe. On dit bonjour, Nina. Bonjour. Tu veux encore jouer ? S'il te plaît. Papa reste tout près. Merci. Bravo, Nina. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, papa. Le fil d'argent de l'escargot reste dans sa tête.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,10 +16947,31 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Zoé rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le soir. Zoé a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Zoé a entendu : bonjour, s'il te plaît, merci. Zoé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une petite lampe fait un rond jaune.
+narrateur|Les chaussons sont près de la porte.
+narrateur|Nina a la dînette, dans la chambre.
+narrateur|La tasse est près des chaussons, sous la lampe.
+maman|On dit bonjour, Nina.
+enfant-f|Bonjour.
+papa|Tu veux encore jouer ?
+enfant-f|S'il te plaît.
+narrateur|Papa reste tout près.
+enfant-f|Merci.
+maman|Bravo, Nina.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, papa.
+narrateur|Le fil d'argent de l'escargot reste dans sa tête.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15852,7 +16996,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina a vécu le soir, dans la chambre. Elle a joué avec la dînette. La petite lampe fait encore un rond jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Nina. Tu as fait du bon travail. Bonne journée, ma grande. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +17136,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Nina a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|La petite lampe fait encore un rond jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-f|Et merci.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, ma grande.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +17167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +17205,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-028.xlsx
+++ b/stories/arbres/TREE-COL-028.xlsx
@@ -2348,17 +2348,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Tu as demandé au bon moment. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.</t>
+          <t>La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Je t'ai entendue, là. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Tu as demandé au bon moment. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Je t'ai entendue, là. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Tu as demandé au bon moment. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;La boîte du goûter est près de la casserole. Le couvercle est tiède, un peu collant. Je la prends ! Nina avance la main. La chaleur la fait reculer. Maman parle du lait, sans se presser. Nina attend la fin de la phrase. Le goûter, s'il te plaît. Le voilà, il a refroidi. Merci. Je t'ai entendue, là. La boîte glisse dans le cartable, toc. Une odeur de cacao reste sur le couvercle.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
 enfant-f|Le goûter, s'il te plaît.
 maman|Le voilà, il a refroidi.
 enfant-f|Merci.
-papa|Tu as demandé au bon moment.
+papa|Je t'ai entendue, là.
 narrateur|La boîte glisse dans le cartable, toc.
 narrateur|Une odeur de cacao reste sur le couvercle.</t>
         </is>
@@ -2923,17 +2923,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Tu l'as demandé. Bravo, Nina. Derrière elle, la vitre de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.</t>
+          <t>Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Il tient bien, au dos. Bravo, Nina. Derrière elle, la vitre de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Tu l'as demandé. Bravo, Nina. Derrière elle, la &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Il tient bien, au dos. Bravo, Nina. Derrière elle, la &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Tu l'as demandé. Bravo, Nina. Derrière elle, la &lt;emphasis&gt;vitre&lt;/emphasis&gt; de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche sur le chemin, le cartable au dos. La boîte fait un petit toc, à chaque pas. Il est à moi. Il tient bien, au dos. Bravo, Nina. Derrière elle, la &lt;emphasis&gt;vitre&lt;/emphasis&gt; de la cuisine est nette. Une miette dorée brille sur la boucle. Le rond de manche n'est plus un nuage.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
           <t>narrateur|Nina marche sur le chemin, le cartable au dos.
 narrateur|La boîte fait un petit toc, à chaque pas.
 enfant-f|Il est à moi.
-papa|Tu l'as demandé.
+papa|Il tient bien, au dos.
 maman|Bravo, Nina.
 narrateur|Derrière elle, la vitre de la cuisine est nette.
 narrateur|Une miette dorée brille sur la boucle.
@@ -3296,17 +3296,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci d'avoir attendu. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.</t>
+          <t>Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci, on n'est pas pressés. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci d'avoir attendu. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci, on n'est pas pressés. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci d'avoir attendu. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina s'assoit près du bol, le cartable contre elle. La boîte est tiède, au fond. On partira plus tard. Oui. Merci, on n'est pas pressés. Un carré de soleil a fini de sécher le verre. Plus de voix dans le cacao. Ce jaune-là est devenu mat, paisible.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
 narrateur|La boîte est tiède, au fond.
 enfant-f|On partira plus tard.
 maman|Oui.
-papa|Merci d'avoir attendu.
+papa|Merci, on n'est pas pressés.
 narrateur|Un carré de soleil a fini de sécher le verre.
 narrateur|Plus de voix dans le cacao.
 narrateur|Ce jaune-là est devenu mat, paisible.</t>
@@ -4429,17 +4429,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci de l'avoir glissée sans la froisser. Le toit de la classe grandit. La vitre, derrière, garde un ovale clair. Plus de papier collé au verre.</t>
+          <t>Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci, le papier n'a pas de pli. Le toit de la classe grandit. La vitre, derrière, garde un ovale clair. Plus de papier collé au verre.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci de l'avoir glissée sans la froisser. Le toit de la classe grandit. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt;, derrière, garde un ovale clair. Plus de papier collé au verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci, le papier n'a pas de pli. Le toit de la classe grandit. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt;, derrière, garde un ovale clair. Plus de papier collé au verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci de l'avoir glissée sans la froisser. Le toit de la classe grandit. La &lt;emphasis&gt;vitre&lt;/emphasis&gt;, derrière, garde un ovale clair. Plus de papier collé au verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sur le chemin, la poche frotte un peu le dos de Nina. Le dessin est là, droit. La maison jaune vient avec moi. Je l'ai vue. Merci, le papier n'a pas de pli. Le toit de la classe grandit. La &lt;emphasis&gt;vitre&lt;/emphasis&gt;, derrière, garde un ovale clair. Plus de papier collé au verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
 narrateur|Le dessin est là, droit.
 enfant-f|La maison jaune vient avec moi.
 maman|Je l'ai vue.
-papa|Merci de l'avoir glissée sans la froisser.
+papa|Merci, le papier n'a pas de pli.
 narrateur|Le toit de la classe grandit.
 narrateur|La vitre, derrière, garde un ovale clair.
 narrateur|Plus de papier collé au verre.</t>
@@ -4801,17 +4801,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Merci d'avoir lissé sans casser. La vitre n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.</t>
+          <t>Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Ta maison est droite, merci. La vitre n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Merci d'avoir lissé sans casser. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Ta maison est droite, merci. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Merci d'avoir lissé sans casser. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina pose le cartable près du bol. Le coin du dessin n'est plus mouillé. Elle est droite, ma maison. Oui. Ta maison est droite, merci. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; n'a plus de larmes. Un rond clair reste, comme une fenêtre dans la fenêtre. Le chemin attend, sans se presser.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -4953,7 +4953,7 @@
 narrateur|Le coin du dessin n'est plus mouillé.
 enfant-f|Elle est droite, ma maison.
 papa|Oui.
-maman|Merci d'avoir lissé sans casser.
+maman|Ta maison est droite, merci.
 narrateur|La vitre n'a plus de larmes.
 narrateur|Un rond clair reste, comme une fenêtre dans la fenêtre.
 narrateur|Le chemin attend, sans se presser.</t>
@@ -5934,17 +5934,17 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci d'avoir guidé le geste. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.</t>
+          <t>Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci, on a vu le chemin ensemble. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci d'avoir guidé le geste. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci, on a vu le chemin ensemble. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci d'avoir guidé le geste. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina passe l'ovale, le cartable au dos. Le torchon reste sur la chaise, taché d'un peu de jaune. Je vois le chemin. Nous aussi. Merci, on a vu le chemin ensemble. L'ovale encadre la haie, puis se perd. Le toit de la classe est net. Le cacao n'embue plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
 narrateur|Le torchon reste sur la chaise, taché d'un peu de jaune.
 enfant-f|Je vois le chemin.
 papa|Nous aussi.
-maman|Merci d'avoir guidé le geste.
+maman|Merci, on a vu le chemin ensemble.
 narrateur|L'ovale encadre la haie, puis se perd.
 narrateur|Le toit de la classe est net.
 narrateur|Le cacao n'embue plus rien.</t>
@@ -6307,17 +6307,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci d'avoir regardé d'abord. Le torchon sent le four, sur la chaise. La vitre est un miroir, sans travail. Le cartable attend près du bol, prêt.</t>
+          <t>Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci, tes yeux ont suffi. Le torchon sent le four, sur la chaise. La vitre est un miroir, sans travail. Le cartable attend près du bol, prêt.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci d'avoir regardé d'abord. Le torchon sent le four, sur la chaise. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; est un miroir, sans travail. Le cartable attend près du bol, prêt.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci, tes yeux ont suffi. Le torchon sent le four, sur la chaise. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; est un miroir, sans travail. Le cartable attend près du bol, prêt.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci d'avoir regardé d'abord. Le torchon sent le four, sur la chaise. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; est un miroir, sans travail. Le cartable attend près du bol, prêt.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina n'a pas frotté. Le chemin était là, sans elle. Le torchon se repose. Oui. Merci, tes yeux ont suffi. Le torchon sent le four, sur la chaise. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; est un miroir, sans travail. Le cartable attend près du bol, prêt.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -6459,7 +6459,7 @@
 narrateur|Le chemin était là, sans elle.
 enfant-f|Le torchon se repose.
 maman|Oui.
-papa|Merci d'avoir regardé d'abord.
+papa|Merci, tes yeux ont suffi.
 narrateur|Le torchon sent le four, sur la chaise.
 narrateur|La vitre est un miroir, sans travail.
 narrateur|Le cartable attend près du bol, prêt.</t>
@@ -6678,17 +6678,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci d'avoir posé le tissu ailleurs. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.</t>
+          <t>Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci, la lampe reste libre. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci d'avoir posé le tissu ailleurs. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci, la lampe reste libre. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci d'avoir posé le tissu ailleurs. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le torchon est sur le dossier, loin de la lampe. Le cartable dort contre le verre. Le jaune fait une lune. Je la vois. Merci, la lampe reste libre. La buée tient autour de l'ovale, sans le manger. Le chemin de l'école est une ligne noire. La casserole est vide, tiède.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6830,7 +6830,7 @@
 narrateur|Le cartable dort contre le verre.
 enfant-f|Le jaune fait une lune.
 papa|Je la vois.
-maman|Merci d'avoir posé le tissu ailleurs.
+maman|Merci, la lampe reste libre.
 narrateur|La buée tient autour de l'ovale, sans le manger.
 narrateur|Le chemin de l'école est une ligne noire.
 narrateur|La casserole est vide, tiède.</t>
@@ -8195,17 +8195,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci d'avoir fermé avant de courir. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.</t>
+          <t>Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci, la fermeture tient. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci d'avoir fermé avant de courir. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci, la fermeture tient. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci d'avoir fermé avant de courir. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche, la boîte au dos, toc, toc. La feuille reste au crochet, comme un ticket oublié. Mon cartable ne glisse plus. La courroie est sèche. Merci, la fermeture tient. Les dalles ne sont plus des cuillères. Le chemin brille, puis devient poussière claire. Le jardin reste derrière, mouillé et calme.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8347,7 +8347,7 @@
 narrateur|La feuille reste au crochet, comme un ticket oublié.
 enfant-f|Mon cartable ne glisse plus.
 papa|La courroie est sèche.
-maman|Merci d'avoir fermé avant de courir.
+maman|Merci, la fermeture tient.
 narrateur|Les dalles ne sont plus des cuillères.
 narrateur|Le chemin brille, puis devient poussière claire.
 narrateur|Le jardin reste derrière, mouillé et calme.</t>
@@ -8568,17 +8568,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci d'avoir attendu l'abeille. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.</t>
+          <t>L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci, l'abeille est partie. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci d'avoir attendu l'abeille. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci, l'abeille est partie. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci d'avoir attendu l'abeille. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'abeille a quitté le thym. Nina tient le cartable à l'ombre du mur. Le goûter est tiède. Oui. Merci, l'abeille est partie. La table du jardin est sèche, presque blanche. Le couvercle sent l'herbe et le soleil. Le chemin, plus loin, ne dit rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -8720,7 +8720,7 @@
 narrateur|Nina tient le cartable à l'ombre du mur.
 enfant-f|Le goûter est tiède.
 maman|Oui.
-papa|Merci d'avoir attendu l'abeille.
+papa|Merci, l'abeille est partie.
 narrateur|La table du jardin est sèche, presque blanche.
 narrateur|Le couvercle sent l'herbe et le soleil.
 narrateur|Le chemin, plus loin, ne dit rien.</t>
@@ -8940,17 +8940,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci d'avoir demandé le décrochage. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.</t>
+          <t>Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci, Nina. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci d'avoir demandé le décrochage. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci, Nina. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci d'avoir demandé le décrochage. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable est rentré, la boîte dedans. Le crochet de la porte est vide. Une étoile dans la goutte. Je la vois. Merci, Nina. Le carré jaune a quitté la porte. Il est dans la cuisine, près des clés. Le jardin respire, sans le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9092,7 +9092,7 @@
 narrateur|Le crochet de la porte est vide.
 enfant-f|Une étoile dans la goutte.
 papa|Je la vois.
-maman|Merci d'avoir demandé le décrochage.
+maman|Merci, Nina.
 narrateur|Le carré jaune a quitté la porte.
 narrateur|Il est dans la cuisine, près des clés.
 narrateur|Le jardin respire, sans le sac.</t>
@@ -9699,17 +9699,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci d'avoir gardé le papier. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.</t>
+          <t>Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci, le papier est au chaud. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci d'avoir gardé le papier. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci, le papier est au chaud. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci d'avoir gardé le papier. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina marche, le dessin au chaud dans la poche. L'oiseau a quitté la haie. Je lui ai dit bonjour. Il a dû entendre. Merci, le papier est au chaud. Une goutte reste au milieu du chemin, puis sèche. Le thym colle aux doigts. Le jaune avance, sans voler.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -9851,7 +9851,7 @@
 narrateur|L'oiseau a quitté la haie.
 enfant-f|Je lui ai dit bonjour.
 maman|Il a dû entendre.
-papa|Merci d'avoir gardé le papier.
+papa|Merci, le papier est au chaud.
 narrateur|Une goutte reste au milieu du chemin, puis sèche.
 narrateur|Le thym colle aux doigts.
 narrateur|Le jaune avance, sans voler.</t>
@@ -10070,17 +10070,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci de l'avoir laissée. La vitre de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.</t>
+          <t>La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci, l'herbe garde son voyage. La vitre de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci de l'avoir laissée. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci, l'herbe garde son voyage. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci de l'avoir laissée. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La veine d'herbe reste sur le papier, dans la poche. Nina s'assoit sur le seuil. C'est son voyage. Oui. Merci, l'herbe garde son voyage. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; de la porte montre le banc, net. Le cartable est chaud, contre la jambe. Le chemin attend, large et pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -10222,7 +10222,7 @@
 narrateur|Nina s'assoit sur le seuil.
 enfant-f|C'est son voyage.
 papa|Oui.
-maman|Merci de l'avoir laissée.
+maman|Merci, l'herbe garde son voyage.
 narrateur|La vitre de la porte montre le banc, net.
 narrateur|Le cartable est chaud, contre la jambe.
 narrateur|Le chemin attend, large et pâle.</t>
@@ -10442,17 +10442,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci d'avoir parlé sans ouvrir. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.</t>
+          <t>Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci, le papillon a eu sa phrase. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci d'avoir parlé sans ouvrir. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci, le papillon a eu sa phrase. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci d'avoir parlé sans ouvrir. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Plus de papillon au verre. Contre le carton, le dessin dort. Bonjour, haie. Elle ne répond pas, c'est normal. Merci, le papillon a eu sa phrase. Le cartable est dans la maison, sentant le thym. La porte du jardin est noire, un peu froide. Une aile a laissé une poussière d'or, minuscule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10594,7 +10594,7 @@
 narrateur|Contre le carton, le dessin dort.
 enfant-f|Bonjour, haie.
 maman|Elle ne répond pas, c'est normal.
-papa|Merci d'avoir parlé sans ouvrir.
+papa|Merci, le papillon a eu sa phrase.
 narrateur|Le cartable est dans la maison, sentant le thym.
 narrateur|La porte du jardin est noire, un peu froide.
 narrateur|Une aile a laissé une poussière d'or, minuscule.</t>
@@ -11201,17 +11201,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci d'avoir demandé l'aide. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.</t>
+          <t>Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci, tes épaules sont prêtes. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci d'avoir demandé l'aide. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci, tes épaules sont prêtes. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci d'avoir demandé l'aide. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina a le cartable sur les épaules, un bras, puis l'autre. Le torchon flotte un peu, sur la corde. Ça ne glisse plus. La courroie est sèche. Merci, tes épaules sont prêtes. Les dalles sont claires, vides. Le chemin prend le jaune et l'emmène. Le crochet ne pend plus rien.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -11353,7 +11353,7 @@
 narrateur|Le torchon flotte un peu, sur la corde.
 enfant-f|Ça ne glisse plus.
 papa|La courroie est sèche.
-maman|Merci d'avoir demandé l'aide.
+maman|Merci, tes épaules sont prêtes.
 narrateur|Les dalles sont claires, vides.
 narrateur|Le chemin prend le jaune et l'emmène.
 narrateur|Le crochet ne pend plus rien.</t>
@@ -11574,17 +11574,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci d'avoir choisi la marche. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.</t>
+          <t>Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci, la marche le garde. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci d'avoir choisi la marche. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci, la marche le garde. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci d'avoir choisi la marche. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le torchon est sur la marche, plié. Le cartable dort contre le mur, à l'ombre. Le lézard est parti. Oui. Merci, la marche le garde. Les dalles tiennent les pieds, sans glisser. Une feuille sèche tremble, puis s'arrête. Le jaune du mur est plus pâle que le sac.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11726,7 +11726,7 @@
 narrateur|Le cartable dort contre le mur, à l'ombre.
 enfant-f|Le lézard est parti.
 maman|Oui.
-papa|Merci d'avoir choisi la marche.
+papa|Merci, la marche le garde.
 narrateur|Les dalles tiennent les pieds, sans glisser.
 narrateur|Une feuille sèche tremble, puis s'arrête.
 narrateur|Le jaune du mur est plus pâle que le sac.</t>
@@ -11945,17 +11945,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci d'avoir tenu le sac. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.</t>
+          <t>Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci, le sac est rentré. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci d'avoir tenu le sac. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci, le sac est rentré. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci d'avoir tenu le sac. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable rentre, sentant le jardin et le torchon. Un rond de lampe reste sur la porte. Le crochet est vide. Oui. Merci, le sac est rentré. Nina a les doigts un peu rèches, de la toile. La nuit a pris le chemin. Le jaune est à l'intérieur, enfin.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12097,7 +12097,7 @@
 narrateur|Un rond de lampe reste sur la porte.
 enfant-f|Le crochet est vide.
 papa|Oui.
-maman|Merci d'avoir tenu le sac.
+maman|Merci, le sac est rentré.
 narrateur|Nina a les doigts un peu rèches, de la toile.
 narrateur|La nuit a pris le chemin.
 narrateur|Le jaune est à l'intérieur, enfin.</t>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci d'avoir attendu. La vitre montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.</t>
+          <t>Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci, on peut partir. La vitre montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci d'avoir attendu. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci, on peut partir. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci d'avoir attendu. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina quitte la chambre, le cartable un peu lourd. Le pull garde son creux, sur le lit. Les chaussettes sont chaudes. Oui. Merci, on peut partir. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; montre le chemin, sans buée. La chaise est vide, un peu chaude. La boîte tape le dos, toc, vers l'école.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13612,7 +13612,7 @@
 narrateur|Le pull garde son creux, sur le lit.
 enfant-f|Les chaussettes sont chaudes.
 maman|Oui.
-papa|Merci d'avoir attendu.
+papa|Merci, on peut partir.
 narrateur|La vitre montre le chemin, sans buée.
 narrateur|La chaise est vide, un peu chaude.
 narrateur|La boîte tape le dos, toc, vers l'école.</t>
@@ -13832,17 +13832,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci d'avoir demandé avant de sortir. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.</t>
+          <t>Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci, on l'entend bien. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci d'avoir demandé avant de sortir. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci, on l'entend bien. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci d'avoir demandé avant de sortir. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Nina écoute le toc, au fond du cartable. La boîte est là, pour plus tard. Je l'ai entendue. Moi aussi. Merci, on l'entend bien. L'oreiller reprend sa forme, lentement. Un grain de soleil tient sur la fermeture. La chaise garde le jaune, comme un ami.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -13984,7 +13984,7 @@
 narrateur|La boîte est là, pour plus tard.
 enfant-f|Je l'ai entendue.
 papa|Moi aussi.
-maman|Merci d'avoir demandé avant de sortir.
+maman|Merci, on l'entend bien.
 narrateur|L'oreiller reprend sa forme, lentement.
 narrateur|Un grain de soleil tient sur la fermeture.
 narrateur|La chaise garde le jaune, comme un ami.</t>
@@ -14203,17 +14203,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci d'avoir refermé. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.</t>
+          <t>Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci, la boîte est close. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci d'avoir refermé. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci, la boîte est close. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci d'avoir refermé. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Une miette a goûté le soir, une seule. La boîte est refermée. Demain. Demain. Merci, la boîte est close. La veilleuse tient le cartable d'or. Le verre de la chambre est une nuit calme. Le pull, sur le lit, n'a plus de secret.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -14355,7 +14355,7 @@
 narrateur|La boîte est refermée.
 enfant-f|Demain.
 maman|Demain.
-papa|Merci d'avoir refermé.
+papa|Merci, la boîte est close.
 narrateur|La veilleuse tient le cartable d'or.
 narrateur|Le verre de la chambre est une nuit calme.
 narrateur|Le pull, sur le lit, n'a plus de secret.</t>
@@ -14962,17 +14962,17 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. Non. Merci d'avoir demandé la poche. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.</t>
+          <t>La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. C'est vrai. Merci, la poche la garde. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. Non. Merci d'avoir demandé la poche. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. C'est vrai. Merci, la poche la garde. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. Non. Merci d'avoir demandé la poche. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La cloche lointaine a fini. La maison jaune voyage dans la poche. Elle n'est plus sous le lit. C'est vrai. Merci, la poche la garde. La chaussette reste seule, sous le bois. La chaise est vide. Le chemin entre dans les yeux de Nina, clair.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -15113,8 +15113,8 @@
           <t>narrateur|La cloche lointaine a fini.
 narrateur|La maison jaune voyage dans la poche.
 enfant-f|Elle n'est plus sous le lit.
-papa|Non.
-maman|Merci d'avoir demandé la poche.
+papa|C'est vrai.
+maman|Merci, la poche la garde.
 narrateur|La chaussette reste seule, sous le bois.
 narrateur|La chaise est vide.
 narrateur|Le chemin entre dans les yeux de Nina, clair.</t>
@@ -15334,17 +15334,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la vitre, dans le sac. Oui. Merci d'avoir choisi. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.</t>
+          <t>La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la vitre, dans le sac. Oui. Merci, la poche a gagné. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt;, dans le sac. Oui. Merci d'avoir choisi. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt;, dans le sac. Oui. Merci, la poche a gagné. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la &lt;emphasis&gt;vitre&lt;/emphasis&gt;, dans le sac. Oui. Merci d'avoir choisi. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La poussière est retombée. Le dessin est dans la poche, tiède. Pas à la &lt;emphasis&gt;vitre&lt;/emphasis&gt;, dans le sac. Oui. Merci, la poche a gagné. Le cartable, sur la chaise, a l'air prêt. Un dernier grain brille, puis plus rien. Le chemin, dehors, attend sans frapper au verre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -15486,7 +15486,7 @@
 narrateur|Le dessin est dans la poche, tiède.
 enfant-f|Pas à la vitre, dans le sac.
 maman|Oui.
-papa|Merci d'avoir choisi.
+papa|Merci, la poche a gagné.
 narrateur|Le cartable, sur la chaise, a l'air prêt.
 narrateur|Un dernier grain brille, puis plus rien.
 narrateur|Le chemin, dehors, attend sans frapper au verre.</t>
@@ -16464,17 +16464,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci de t'être arrêtée. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.</t>
+          <t>L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci, l'ovale reste. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci de t'être arrêtée. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci, l'ovale reste. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci de t'être arrêtée. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'ovale en forme de maison cadre le chemin. Nina ne frotte plus. Si je frotte, il part. Oui. Merci, l'ovale reste. Le torchon reste sur le radiateur, inutile. Le cartable quitte la chaise, jaune et net. Le tic du radiateur s'est tu.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
 narrateur|Nina ne frotte plus.
 enfant-f|Si je frotte, il part.
 maman|Oui.
-papa|Merci de t'être arrêtée.
+papa|Merci, l'ovale reste.
 narrateur|Le torchon reste sur le radiateur, inutile.
 narrateur|Le cartable quitte la chaise, jaune et net.
 narrateur|Le tic du radiateur s'est tu.</t>
@@ -16836,17 +16836,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci d'avoir demandé qu'on le tende. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La vitre sèche garde le chemin, sans ovale.</t>
+          <t>Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci, il est à toi. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La vitre sèche garde le chemin, sans ovale.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci d'avoir demandé qu'on le tende. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; sèche garde le chemin, sans ovale.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci, il est à toi. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La &lt;emphasis level="moderate"&gt;vitre&lt;/emphasis&gt; sèche garde le chemin, sans ovale.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci d'avoir demandé qu'on le tende. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; sèche garde le chemin, sans ovale.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le cartable n'est plus un chat, il est sur le dos. Le radiateur fait un dernier tic. Il était prêt. Oui. Merci, il est à toi. Le torchon n'a plus de travail. Un rayon a quitté la boucle. La &lt;emphasis&gt;vitre&lt;/emphasis&gt; sèche garde le chemin, sans ovale.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
@@ -16988,7 +16988,7 @@
 narrateur|Le radiateur fait un dernier tic.
 enfant-f|Il était prêt.
 papa|Oui.
-maman|Merci d'avoir demandé qu'on le tende.
+maman|Merci, il est à toi.
 narrateur|Le torchon n'a plus de travail.
 narrateur|Un rayon a quitté la boucle.
 narrateur|La vitre sèche garde le chemin, sans ovale.</t>
@@ -17388,7 +17388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17445,6 +17445,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
